--- a/output/AAPL_dcf_model.xlsx
+++ b/output/AAPL_dcf_model.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B23">
-        <f>H20/(B$5-B$6)</f>
+        <f>H20/($B$5-$B$6)</f>
         <v/>
       </c>
     </row>

--- a/output/AAPL_dcf_model.xlsx
+++ b/output/AAPL_dcf_model.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="$0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -67,12 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -583,7 +585,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>391035000000</v>
       </c>
       <c r="C13">
         <f>B13*(1+$B$4)</f>
@@ -869,7 +871,7 @@
         </is>
       </c>
       <c r="B23">
-        <f>H20/($B$5-$B$6)</f>
+        <f>H20/($B$5-$B$7)</f>
         <v/>
       </c>
     </row>
@@ -880,7 +882,7 @@
         </is>
       </c>
       <c r="B24">
-        <f>B23/((1+$B$6)^5)</f>
+        <f>B23/((1+$B$7)^5)</f>
         <v/>
       </c>
     </row>
@@ -891,7 +893,7 @@
         </is>
       </c>
       <c r="B25">
-        <f>NPV($B$6,C20:G20)</f>
+        <f>NPV($B$7,C20:G20)</f>
         <v/>
       </c>
     </row>
@@ -1037,6 +1039,34 @@
           <t>1%</t>
         </is>
       </c>
+      <c r="B3" s="5">
+        <f>((DCF Model.H20/0.01-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="C3" s="5">
+        <f>((DCF Model.H20/0.01-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="D3" s="5">
+        <f>((DCF Model.H20/0.01-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="E3" s="5">
+        <f>((DCF Model.H20/0.01-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="F3" s="5">
+        <f>((DCF Model.H20/0.01-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="G3" s="5">
+        <f>((DCF Model.H20/0.01-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="H3" s="5">
+        <f>((DCF Model.H20/0.01-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1044,6 +1074,34 @@
           <t>2%</t>
         </is>
       </c>
+      <c r="B4" s="5">
+        <f>((DCF Model.H20/0.02-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>((DCF Model.H20/0.02-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>((DCF Model.H20/0.02-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>((DCF Model.H20/0.02-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>((DCF Model.H20/0.02-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>((DCF Model.H20/0.02-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>((DCF Model.H20/0.02-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1051,6 +1109,34 @@
           <t>3%</t>
         </is>
       </c>
+      <c r="B5" s="5">
+        <f>((DCF Model.H20/0.03-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>((DCF Model.H20/0.03-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>((DCF Model.H20/0.03-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>((DCF Model.H20/0.03-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="F5" s="5">
+        <f>((DCF Model.H20/0.03-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="G5" s="5">
+        <f>((DCF Model.H20/0.03-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
+        <f>((DCF Model.H20/0.03-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1058,6 +1144,34 @@
           <t>4%</t>
         </is>
       </c>
+      <c r="B6" s="5">
+        <f>((DCF Model.H20/0.04-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="C6" s="5">
+        <f>((DCF Model.H20/0.04-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>((DCF Model.H20/0.04-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="E6" s="5">
+        <f>((DCF Model.H20/0.04-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="F6" s="5">
+        <f>((DCF Model.H20/0.04-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="G6" s="5">
+        <f>((DCF Model.H20/0.04-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="H6" s="5">
+        <f>((DCF Model.H20/0.04-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1065,8 +1179,48 @@
           <t>5%</t>
         </is>
       </c>
+      <c r="B7" s="5">
+        <f>((DCF Model.H20/0.05-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>((DCF Model.H20/0.05-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>((DCF Model.H20/0.05-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>((DCF Model.H20/0.05-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>((DCF Model.H20/0.05-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>((DCF Model.H20/0.05-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>((DCF Model.H20/0.05-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B3:H7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00FF6B6B"/>
+        <color rgb="00FFEB3B"/>
+        <color rgb="004CAF50"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/AAPL_dcf_model.xlsx
+++ b/output/AAPL_dcf_model.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -42,7 +56,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,12 +65,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,16 +84,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick"/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom style="thick"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -440,540 +469,586 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AAPL - Discounted Cash Flow Model</t>
+          <t>Discounted Cash Flow Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ticker Symbol:</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>To analyze a new symbol:</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. Change symbol in B2</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2. Run: python examples/analyze_stock.py [NEW_SYMBOL]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Key Assumptions</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Data Source: Yahoo Finance &amp; Financial Modeling Prep</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Revenue Growth Rate (Years 1-5)</t>
+          <t>Company Name:</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3%</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WACC (Discount Rate)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>10%</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Key Assumptions</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>Revenue Growth Rate (Years 1-5)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EBITDA Margin</t>
+          <t>Terminal Growth Rate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capex as % of Revenue</t>
+          <t>WACC (Discount Rate)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Working Capital Change</t>
+          <t>Tax Rate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Terminal</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex as % of Revenue</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>391035000000</v>
-      </c>
-      <c r="C13">
-        <f>B13*(1+$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>C13*(1+$B$4)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>D13*(1+$B$4)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>E13*(1+$B$4)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13*(1+$B$4)</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>G13*(1+$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B14">
-        <f>B13*$B$7</f>
-        <v/>
-      </c>
-      <c r="C14">
-        <f>C13*$B$7</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>D13*$B$7</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>E13*$B$7</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>F13*$B$7</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>G13*$B$7</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>H13*$B$7</f>
-        <v/>
+          <t>Working Capital Change</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B15">
-        <f>B14</f>
-        <v/>
-      </c>
-      <c r="C15">
-        <f>C14</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="F15">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>H14</f>
-        <v/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="B16">
-        <f>B15*$B$6</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>391035000000</v>
       </c>
       <c r="C16">
-        <f>C15*$B$6</f>
+        <f>B16*(1+$B$7)</f>
         <v/>
       </c>
       <c r="D16">
-        <f>D15*$B$6</f>
+        <f>C16*(1+$B$7)</f>
         <v/>
       </c>
       <c r="E16">
-        <f>E15*$B$6</f>
+        <f>D16*(1+$B$7)</f>
         <v/>
       </c>
       <c r="F16">
-        <f>F15*$B$6</f>
+        <f>E16*(1+$B$7)</f>
         <v/>
       </c>
       <c r="G16">
-        <f>G15*$B$6</f>
+        <f>F16*(1+$B$7)</f>
         <v/>
       </c>
       <c r="H16">
-        <f>H15*$B$6</f>
+        <f>G16*(1+$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOPAT</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="B17">
-        <f>B15-B16</f>
+        <f>B16*$B$10</f>
         <v/>
       </c>
       <c r="C17">
-        <f>C15-C16</f>
+        <f>C16*$B$10</f>
         <v/>
       </c>
       <c r="D17">
-        <f>D15-D16</f>
+        <f>D16*$B$10</f>
         <v/>
       </c>
       <c r="E17">
-        <f>E15-E16</f>
+        <f>E16*$B$10</f>
         <v/>
       </c>
       <c r="F17">
-        <f>F15-F16</f>
+        <f>F16*$B$10</f>
         <v/>
       </c>
       <c r="G17">
-        <f>G15-G16</f>
+        <f>G16*$B$10</f>
         <v/>
       </c>
       <c r="H17">
-        <f>H15-H16</f>
+        <f>H16*$B$10</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capex</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="B18">
-        <f>B13*$B$8</f>
+        <f>B17</f>
         <v/>
       </c>
       <c r="C18">
-        <f>C13*$B$8</f>
+        <f>C17</f>
         <v/>
       </c>
       <c r="D18">
-        <f>D13*$B$8</f>
+        <f>D17</f>
         <v/>
       </c>
       <c r="E18">
-        <f>E13*$B$8</f>
+        <f>E17</f>
         <v/>
       </c>
       <c r="F18">
-        <f>F13*$B$8</f>
+        <f>F17</f>
         <v/>
       </c>
       <c r="G18">
-        <f>G13*$B$8</f>
+        <f>G17</f>
         <v/>
       </c>
       <c r="H18">
-        <f>H13*$B$8</f>
+        <f>H17</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Working Capital Change</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="B19">
-        <f>B13*$B$9</f>
+        <f>B18*$B$9</f>
         <v/>
       </c>
       <c r="C19">
-        <f>C13*$B$9</f>
+        <f>C18*$B$9</f>
         <v/>
       </c>
       <c r="D19">
-        <f>D13*$B$9</f>
+        <f>D18*$B$9</f>
         <v/>
       </c>
       <c r="E19">
-        <f>E13*$B$9</f>
+        <f>E18*$B$9</f>
         <v/>
       </c>
       <c r="F19">
-        <f>F13*$B$9</f>
+        <f>F18*$B$9</f>
         <v/>
       </c>
       <c r="G19">
-        <f>G13*$B$9</f>
+        <f>G18*$B$9</f>
         <v/>
       </c>
       <c r="H19">
-        <f>H13*$B$9</f>
+        <f>H18*$B$9</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Free Cash Flow</t>
+          <t>NOPAT</t>
         </is>
       </c>
       <c r="B20">
-        <f>B17-B18-B19</f>
+        <f>B18-B19</f>
         <v/>
       </c>
       <c r="C20">
-        <f>C17-C18-C19</f>
+        <f>C18-C19</f>
         <v/>
       </c>
       <c r="D20">
-        <f>D17-D18-D19</f>
+        <f>D18-D19</f>
         <v/>
       </c>
       <c r="E20">
-        <f>E17-E18-E19</f>
+        <f>E18-E19</f>
         <v/>
       </c>
       <c r="F20">
-        <f>F17-F18-F19</f>
+        <f>F18-F19</f>
         <v/>
       </c>
       <c r="G20">
-        <f>G17-G18-G19</f>
+        <f>G18-G19</f>
         <v/>
       </c>
       <c r="H20">
-        <f>H17-H18-H19</f>
+        <f>H18-H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>B16*$B$11</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>C16*$B$11</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>D16*$B$11</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>E16*$B$11</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>F16*$B$11</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>G16*$B$11</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>H16*$B$11</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Valuation</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Working Capital Change</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>B16*$B$12</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>C16*$B$12</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>D16*$B$12</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>E16*$B$12</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>F16*$B$12</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>G16*$B$12</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>H16*$B$12</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Terminal Value</t>
+          <t>Free Cash Flow</t>
         </is>
       </c>
       <c r="B23">
-        <f>H20/($B$5-$B$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PV of Terminal Value</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>B23/((1+$B$7)^5)</f>
+        <f>B20-B21-B22</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>C20-C21-C22</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>D20-D21-D22</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>E20-E21-E22</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>F20-F21-F22</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>G20-G21-G22</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>H20-H21-H22</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sum of PV of FCF (Years 1-5)</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>NPV($B$7,C20:G20)</f>
-        <v/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Value</t>
+          <t>Terminal Value</t>
         </is>
       </c>
       <c r="B26">
-        <f>B24+B25</f>
+        <f>H23/($B$8-$B$10)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Less: Net Debt</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>76686000000</v>
+          <t>PV of Terminal Value</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>B26/((1+$B$10)^5)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equity Value</t>
+          <t>Sum of PV of FCF (Years 1-5)</t>
         </is>
       </c>
       <c r="B28">
-        <f>B26-B27</f>
+        <f>NPV($B$10,C23:G23)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shares Outstanding</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>14935799649.32752</v>
+          <t>Enterprise Value</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>B27+B28</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DCF Price per Share</t>
-        </is>
-      </c>
-      <c r="B30">
-        <f>B28/B29</f>
-        <v/>
+          <t>Less: Net Debt</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>76686000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Current Price</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>211.16</v>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>B29-B30</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>14935799649.32752</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DCF Price per Share</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>B31/B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>211.16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Upside/Downside</t>
         </is>
       </c>
-      <c r="B32" s="3">
-        <f>(B30-B31)/B31</f>
+      <c r="B35" s="6">
+        <f>(B33-B34)/B34</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -990,221 +1065,221 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DCF Sensitivity Analysis</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="B3" s="5">
-        <f>((DCF Model.H20/0.01-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="C3" s="5">
-        <f>((DCF Model.H20/0.01-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="D3" s="5">
-        <f>((DCF Model.H20/0.01-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="E3" s="5">
-        <f>((DCF Model.H20/0.01-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="F3" s="5">
-        <f>((DCF Model.H20/0.01-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="G3" s="5">
-        <f>((DCF Model.H20/0.01-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="H3" s="5">
-        <f>((DCF Model.H20/0.01-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+      <c r="B3" s="8">
+        <f>((DCF Model.H23/0.01-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="C3" s="8">
+        <f>((DCF Model.H23/0.01-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="D3" s="8">
+        <f>((DCF Model.H23/0.01-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="E3" s="8">
+        <f>((DCF Model.H23/0.01-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="F3" s="8">
+        <f>((DCF Model.H23/0.01-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="G3" s="8">
+        <f>((DCF Model.H23/0.01-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="H3" s="8">
+        <f>((DCF Model.H23/0.01-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="B4" s="5">
-        <f>((DCF Model.H20/0.02-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="C4" s="5">
-        <f>((DCF Model.H20/0.02-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="D4" s="5">
-        <f>((DCF Model.H20/0.02-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="E4" s="5">
-        <f>((DCF Model.H20/0.02-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="F4" s="5">
-        <f>((DCF Model.H20/0.02-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="G4" s="5">
-        <f>((DCF Model.H20/0.02-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="H4" s="5">
-        <f>((DCF Model.H20/0.02-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+      <c r="B4" s="8">
+        <f>((DCF Model.H23/0.02-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="C4" s="8">
+        <f>((DCF Model.H23/0.02-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>((DCF Model.H23/0.02-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="E4" s="8">
+        <f>((DCF Model.H23/0.02-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="F4" s="8">
+        <f>((DCF Model.H23/0.02-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="G4" s="8">
+        <f>((DCF Model.H23/0.02-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="H4" s="8">
+        <f>((DCF Model.H23/0.02-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <f>((DCF Model.H20/0.03-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>((DCF Model.H20/0.03-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="D5" s="5">
-        <f>((DCF Model.H20/0.03-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="E5" s="5">
-        <f>((DCF Model.H20/0.03-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="F5" s="5">
-        <f>((DCF Model.H20/0.03-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="G5" s="5">
-        <f>((DCF Model.H20/0.03-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="H5" s="5">
-        <f>((DCF Model.H20/0.03-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+      <c r="B5" s="8">
+        <f>((DCF Model.H23/0.03-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="C5" s="8">
+        <f>((DCF Model.H23/0.03-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="D5" s="8">
+        <f>((DCF Model.H23/0.03-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>((DCF Model.H23/0.03-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>((DCF Model.H23/0.03-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="G5" s="8">
+        <f>((DCF Model.H23/0.03-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="H5" s="8">
+        <f>((DCF Model.H23/0.03-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <f>((DCF Model.H20/0.04-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="C6" s="5">
-        <f>((DCF Model.H20/0.04-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="D6" s="5">
-        <f>((DCF Model.H20/0.04-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="E6" s="5">
-        <f>((DCF Model.H20/0.04-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="F6" s="5">
-        <f>((DCF Model.H20/0.04-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>((DCF Model.H20/0.04-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="H6" s="5">
-        <f>((DCF Model.H20/0.04-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+      <c r="B6" s="8">
+        <f>((DCF Model.H23/0.04-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="C6" s="8">
+        <f>((DCF Model.H23/0.04-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>((DCF Model.H23/0.04-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>((DCF Model.H23/0.04-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>((DCF Model.H23/0.04-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="G6" s="8">
+        <f>((DCF Model.H23/0.04-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>((DCF Model.H23/0.04-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>((DCF Model.H20/0.05-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="C7" s="5">
-        <f>((DCF Model.H20/0.05-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="D7" s="5">
-        <f>((DCF Model.H20/0.05-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="E7" s="5">
-        <f>((DCF Model.H20/0.05-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="F7" s="5">
-        <f>((DCF Model.H20/0.05-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>((DCF Model.H20/0.05-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
-        <v/>
-      </c>
-      <c r="H7" s="5">
-        <f>((DCF Model.H20/0.05-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C20:G20)-DCF Model.B27)/DCF Model.B29</f>
+      <c r="B7" s="8">
+        <f>((DCF Model.H23/0.05-0.08)/((1+0.08)^5)+NPV(0.08,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="C7" s="8">
+        <f>((DCF Model.H23/0.05-0.09)/((1+0.09)^5)+NPV(0.09,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="D7" s="8">
+        <f>((DCF Model.H23/0.05-0.1)/((1+0.1)^5)+NPV(0.1,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>((DCF Model.H23/0.05-0.11)/((1+0.11)^5)+NPV(0.11,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="F7" s="8">
+        <f>((DCF Model.H23/0.05-0.12)/((1+0.12)^5)+NPV(0.12,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="G7" s="8">
+        <f>((DCF Model.H23/0.05-0.13)/((1+0.13)^5)+NPV(0.13,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
+        <v/>
+      </c>
+      <c r="H7" s="8">
+        <f>((DCF Model.H23/0.05-0.14)/((1+0.14)^5)+NPV(0.14,DCF Model.C23:G23)-DCF Model.B30)/DCF Model.B32</f>
         <v/>
       </c>
     </row>
